--- a/assessment_forms/018_narcissistic_behavior_assessment_quiz--assessment_forms.xlsx
+++ b/assessment_forms/018_narcissistic_behavior_assessment_quiz--assessment_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1098,7 +1098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C89"/>
+  <dimension ref="A1:C88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33" customWidth="1" min="1" max="1"/>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>grandiosity</t>
+          <t>manipulation</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Grandiosity</t>
+          <t>Manipulation</t>
         </is>
       </c>
     </row>
@@ -1182,29 +1182,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>manipulation</t>
+          <t>lack_of_empathy</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Manipulation</t>
+          <t>Lack of Empathy</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>narcissistic_tendencies_choices</t>
+          <t>emotional_reactivity_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>lack_of_empathy</t>
+          <t>very_high</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Lack of Empathy</t>
+          <t>Very High</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>very_high</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Very High</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -1267,29 +1267,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>very_low</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Very Low</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>emotional_reactivity_choices</t>
+          <t>social_dominance_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>very_low</t>
+          <t>very_dominant</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Very Low</t>
+          <t>Very Dominant</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>very_dominant</t>
+          <t>dominant</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Very Dominant</t>
+          <t>Dominant</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>dominant</t>
+          <t>not_very_dominant</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Dominant</t>
+          <t>Not Very Dominant</t>
         </is>
       </c>
     </row>
@@ -1335,29 +1335,29 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>not_very_dominant</t>
+          <t>not_dominant</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Not Very Dominant</t>
+          <t>Not Dominant</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>social_dominance_choices</t>
+          <t>assertiveness_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>not_dominant</t>
+          <t>very_assertive</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Not Dominant</t>
+          <t>Very Assertive</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>very_assertive</t>
+          <t>assertive</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Very Assertive</t>
+          <t>Assertive</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>assertive</t>
+          <t>not_very_assertive</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Assertive</t>
+          <t>Not Very Assertive</t>
         </is>
       </c>
     </row>
@@ -1403,29 +1403,29 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>not_very_assertive</t>
+          <t>not_assertive</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Not Very Assertive</t>
+          <t>Not Assertive</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>assertiveness_choices</t>
+          <t>empathy_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>not_assertive</t>
+          <t>very_high</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Not Assertive</t>
+          <t>Very High</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>very_high</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Very High</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -1488,29 +1488,29 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>very_low</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Very Low</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>empathy_choices</t>
+          <t>self_objectivity_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>very_low</t>
+          <t>very_high</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Very Low</t>
+          <t>Very High</t>
         </is>
       </c>
     </row>
@@ -1522,12 +1522,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>very_high</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Very High</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1539,12 +1539,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1556,12 +1556,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -1573,29 +1573,29 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>very_low</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Very Low</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>self_objectivity_choices</t>
+          <t>personal_growth_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>very_low</t>
+          <t>very_high</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Very Low</t>
+          <t>Very High</t>
         </is>
       </c>
     </row>
@@ -1607,12 +1607,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>very_high</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Very High</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1624,12 +1624,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -1658,29 +1658,29 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>very_low</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Very Low</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>personal_growth_choices</t>
+          <t>self_realism_choices</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>very_low</t>
+          <t>very_high</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Very Low</t>
+          <t>Very High</t>
         </is>
       </c>
     </row>
@@ -1692,12 +1692,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>very_high</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Very High</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1709,12 +1709,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1726,12 +1726,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -1743,29 +1743,29 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>very_low</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Very Low</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>self_realism_choices</t>
+          <t>emotional_stability_choices</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>very_low</t>
+          <t>very_high</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Very Low</t>
+          <t>Very High</t>
         </is>
       </c>
     </row>
@@ -1777,12 +1777,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>very_high</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Very High</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1794,12 +1794,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1811,12 +1811,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -1828,29 +1828,29 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>very_low</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Very Low</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>emotional_stability_choices</t>
+          <t>social_support_choices</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>very_low</t>
+          <t>very_high</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Very Low</t>
+          <t>Very High</t>
         </is>
       </c>
     </row>
@@ -1862,12 +1862,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>very_high</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Very High</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1879,12 +1879,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1896,12 +1896,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -1913,29 +1913,29 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>very_low</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Very Low</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>social_support_choices</t>
+          <t>self_perfectionism_choices</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>very_low</t>
+          <t>very_high</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Very Low</t>
+          <t>Very High</t>
         </is>
       </c>
     </row>
@@ -1947,12 +1947,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>very_high</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Very High</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1964,12 +1964,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1981,12 +1981,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -1998,29 +1998,29 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>very_low</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Very Low</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>self_perfectionism_choices</t>
+          <t>self_control_choices</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>very_low</t>
+          <t>very_high</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Very Low</t>
+          <t>Very High</t>
         </is>
       </c>
     </row>
@@ -2032,12 +2032,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>very_high</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Very High</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -2049,12 +2049,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -2066,12 +2066,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -2083,29 +2083,29 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>very_low</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Very Low</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>self_control_choices</t>
+          <t>self_mastery_choices</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>very_low</t>
+          <t>very_high</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Very Low</t>
+          <t>Very High</t>
         </is>
       </c>
     </row>
@@ -2117,12 +2117,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>very_high</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Very High</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -2134,12 +2134,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -2151,12 +2151,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -2168,29 +2168,29 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>very_low</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Very Low</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>self_mastery_choices</t>
+          <t>self_acceptance_choices</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>very_low</t>
+          <t>very_high</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Very Low</t>
+          <t>Very High</t>
         </is>
       </c>
     </row>
@@ -2202,12 +2202,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>very_high</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Very High</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -2219,12 +2219,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -2236,12 +2236,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -2253,29 +2253,29 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>very_low</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Very Low</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>self_acceptance_choices</t>
+          <t>emotional_regulation_choices</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>very_low</t>
+          <t>very_high</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Very Low</t>
+          <t>Very High</t>
         </is>
       </c>
     </row>
@@ -2287,12 +2287,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>very_high</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Very High</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -2304,12 +2304,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -2321,12 +2321,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -2338,29 +2338,29 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>very_low</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Very Low</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>emotional_regulation_choices</t>
+          <t>self_expression_choices</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>very_low</t>
+          <t>very_high</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Very Low</t>
+          <t>Very High</t>
         </is>
       </c>
     </row>
@@ -2372,12 +2372,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>very_high</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Very High</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -2389,12 +2389,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -2406,12 +2406,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -2423,29 +2423,29 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>very_low</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Very Low</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>self_expression_choices</t>
+          <t>self_regard_choices</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>very_low</t>
+          <t>very_high</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Very Low</t>
+          <t>Very High</t>
         </is>
       </c>
     </row>
@@ -2457,12 +2457,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>very_high</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Very High</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -2474,12 +2474,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -2491,12 +2491,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -2508,29 +2508,29 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>very_low</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Very Low</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>self_regard_choices</t>
+          <t>self_actualization_choices</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>very_low</t>
+          <t>very_high</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Very Low</t>
+          <t>Very High</t>
         </is>
       </c>
     </row>
@@ -2542,12 +2542,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>very_high</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Very High</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -2576,12 +2576,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -2593,27 +2593,10 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>very_low</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>self_actualization_choices</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>very_low</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
         <is>
           <t>Very Low</t>
         </is>
